--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY224"/>
+  <dimension ref="A1:AY240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23622,6 +23622,1600 @@
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>128794471</v>
+      </c>
+      <c r="B225" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q225" t="n">
+        <v>514825</v>
+      </c>
+      <c r="R225" t="n">
+        <v>7090372</v>
+      </c>
+      <c r="S225" t="n">
+        <v>10</v>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT225" t="inlineStr"/>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX225" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>128794465</v>
+      </c>
+      <c r="B226" t="n">
+        <v>91484</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q226" t="n">
+        <v>514919</v>
+      </c>
+      <c r="R226" t="n">
+        <v>7090657</v>
+      </c>
+      <c r="S226" t="n">
+        <v>10</v>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT226" t="inlineStr"/>
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX226" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>128794452</v>
+      </c>
+      <c r="B227" t="n">
+        <v>80194</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q227" t="n">
+        <v>514760</v>
+      </c>
+      <c r="R227" t="n">
+        <v>7090867</v>
+      </c>
+      <c r="S227" t="n">
+        <v>10</v>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT227" t="inlineStr"/>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX227" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>128794451</v>
+      </c>
+      <c r="B228" t="n">
+        <v>80194</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr"/>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q228" t="n">
+        <v>514916</v>
+      </c>
+      <c r="R228" t="n">
+        <v>7090603</v>
+      </c>
+      <c r="S228" t="n">
+        <v>10</v>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>På grangrenar</t>
+        </is>
+      </c>
+      <c r="AD228" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE228" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG228" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT228" t="inlineStr"/>
+      <c r="AW228" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX228" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>128794466</v>
+      </c>
+      <c r="B229" t="n">
+        <v>91484</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr"/>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q229" t="n">
+        <v>514904</v>
+      </c>
+      <c r="R229" t="n">
+        <v>7090715</v>
+      </c>
+      <c r="S229" t="n">
+        <v>10</v>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT229" t="inlineStr"/>
+      <c r="AW229" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX229" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>128794468</v>
+      </c>
+      <c r="B230" t="n">
+        <v>91484</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr"/>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q230" t="n">
+        <v>514537</v>
+      </c>
+      <c r="R230" t="n">
+        <v>7090931</v>
+      </c>
+      <c r="S230" t="n">
+        <v>10</v>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT230" t="inlineStr"/>
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX230" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>128794446</v>
+      </c>
+      <c r="B231" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr"/>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q231" t="n">
+        <v>514919</v>
+      </c>
+      <c r="R231" t="n">
+        <v>7090358</v>
+      </c>
+      <c r="S231" t="n">
+        <v>10</v>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT231" t="inlineStr"/>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX231" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>128794454</v>
+      </c>
+      <c r="B232" t="n">
+        <v>80194</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr"/>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q232" t="n">
+        <v>514732</v>
+      </c>
+      <c r="R232" t="n">
+        <v>7090855</v>
+      </c>
+      <c r="S232" t="n">
+        <v>10</v>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT232" t="inlineStr"/>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX232" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>128794456</v>
+      </c>
+      <c r="B233" t="n">
+        <v>80194</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr"/>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q233" t="n">
+        <v>514879</v>
+      </c>
+      <c r="R233" t="n">
+        <v>7090729</v>
+      </c>
+      <c r="S233" t="n">
+        <v>10</v>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT233" t="inlineStr"/>
+      <c r="AW233" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX233" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>128794470</v>
+      </c>
+      <c r="B234" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr"/>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q234" t="n">
+        <v>514601</v>
+      </c>
+      <c r="R234" t="n">
+        <v>7090341</v>
+      </c>
+      <c r="S234" t="n">
+        <v>10</v>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT234" t="inlineStr"/>
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX234" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>128794474</v>
+      </c>
+      <c r="B235" t="n">
+        <v>88867</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>510</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr"/>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q235" t="n">
+        <v>514403</v>
+      </c>
+      <c r="R235" t="n">
+        <v>7090253</v>
+      </c>
+      <c r="S235" t="n">
+        <v>10</v>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT235" t="inlineStr"/>
+      <c r="AW235" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX235" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>128794457</v>
+      </c>
+      <c r="B236" t="n">
+        <v>56871</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr"/>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q236" t="n">
+        <v>514546</v>
+      </c>
+      <c r="R236" t="n">
+        <v>7090530</v>
+      </c>
+      <c r="S236" t="n">
+        <v>10</v>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT236" t="inlineStr"/>
+      <c r="AW236" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX236" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>128794459</v>
+      </c>
+      <c r="B237" t="n">
+        <v>91484</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr"/>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q237" t="n">
+        <v>514757</v>
+      </c>
+      <c r="R237" t="n">
+        <v>7090358</v>
+      </c>
+      <c r="S237" t="n">
+        <v>10</v>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT237" t="inlineStr"/>
+      <c r="AW237" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX237" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>128794462</v>
+      </c>
+      <c r="B238" t="n">
+        <v>91484</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr"/>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q238" t="n">
+        <v>514979</v>
+      </c>
+      <c r="R238" t="n">
+        <v>7090554</v>
+      </c>
+      <c r="S238" t="n">
+        <v>10</v>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT238" t="inlineStr"/>
+      <c r="AW238" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX238" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>128794447</v>
+      </c>
+      <c r="B239" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr"/>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q239" t="n">
+        <v>514897</v>
+      </c>
+      <c r="R239" t="n">
+        <v>7090722</v>
+      </c>
+      <c r="S239" t="n">
+        <v>10</v>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT239" t="inlineStr"/>
+      <c r="AW239" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX239" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>128794473</v>
+      </c>
+      <c r="B240" t="n">
+        <v>92040</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>760</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr"/>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q240" t="n">
+        <v>514732</v>
+      </c>
+      <c r="R240" t="n">
+        <v>7090857</v>
+      </c>
+      <c r="S240" t="n">
+        <v>10</v>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT240" t="inlineStr"/>
+      <c r="AW240" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX240" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY240" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -23624,10 +23624,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128794471</v>
+        <v>128794465</v>
       </c>
       <c r="B225" t="n">
-        <v>79089</v>
+        <v>91485</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23635,21 +23635,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23659,10 +23659,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>514825</v>
+        <v>514919</v>
       </c>
       <c r="R225" t="n">
-        <v>7090372</v>
+        <v>7090657</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23695,11 +23695,6 @@
       <c r="AA225" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC225" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -23726,10 +23721,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128794465</v>
+        <v>128794471</v>
       </c>
       <c r="B226" t="n">
-        <v>91484</v>
+        <v>79089</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23737,21 +23732,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23761,10 +23756,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>514919</v>
+        <v>514825</v>
       </c>
       <c r="R226" t="n">
-        <v>7090657</v>
+        <v>7090372</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23797,6 +23792,11 @@
       <c r="AA226" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -23920,10 +23920,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128794451</v>
+        <v>128794466</v>
       </c>
       <c r="B228" t="n">
-        <v>80194</v>
+        <v>91485</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -23931,21 +23931,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23955,10 +23955,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>514916</v>
+        <v>514904</v>
       </c>
       <c r="R228" t="n">
-        <v>7090603</v>
+        <v>7090715</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23991,11 +23991,6 @@
       <c r="AA228" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC228" t="inlineStr">
-        <is>
-          <t>På grangrenar</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -24022,10 +24017,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>128794466</v>
+        <v>128794451</v>
       </c>
       <c r="B229" t="n">
-        <v>91484</v>
+        <v>80194</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24033,21 +24028,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -24057,10 +24052,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>514904</v>
+        <v>514916</v>
       </c>
       <c r="R229" t="n">
-        <v>7090715</v>
+        <v>7090603</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24093,6 +24088,11 @@
       <c r="AA229" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>På grangrenar</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -24122,7 +24122,7 @@
         <v>128794468</v>
       </c>
       <c r="B230" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128794454</v>
+        <v>128794456</v>
       </c>
       <c r="B232" t="n">
         <v>80194</v>
@@ -24353,10 +24353,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>514732</v>
+        <v>514879</v>
       </c>
       <c r="R232" t="n">
-        <v>7090855</v>
+        <v>7090729</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24389,6 +24389,11 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24415,7 +24420,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128794456</v>
+        <v>128794454</v>
       </c>
       <c r="B233" t="n">
         <v>80194</v>
@@ -24450,10 +24455,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>514879</v>
+        <v>514732</v>
       </c>
       <c r="R233" t="n">
-        <v>7090729</v>
+        <v>7090855</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24486,11 +24491,6 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -24828,7 +24828,7 @@
         <v>128794459</v>
       </c>
       <c r="B237" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>128794462</v>
       </c>
       <c r="B238" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>128794473</v>
       </c>
       <c r="B240" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -23627,7 +23627,7 @@
         <v>128794465</v>
       </c>
       <c r="B225" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23724,7 +23724,7 @@
         <v>128794471</v>
       </c>
       <c r="B226" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>128794452</v>
       </c>
       <c r="B227" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>128794466</v>
       </c>
       <c r="B228" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>128794451</v>
       </c>
       <c r="B229" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>128794468</v>
       </c>
       <c r="B230" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24216,10 +24216,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128794446</v>
+        <v>128794456</v>
       </c>
       <c r="B231" t="n">
-        <v>57689</v>
+        <v>80221</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24227,21 +24227,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -24251,10 +24251,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>514919</v>
+        <v>514879</v>
       </c>
       <c r="R231" t="n">
-        <v>7090358</v>
+        <v>7090729</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24291,7 +24291,7 @@
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24318,10 +24318,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128794456</v>
+        <v>128794454</v>
       </c>
       <c r="B232" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24353,10 +24353,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>514879</v>
+        <v>514732</v>
       </c>
       <c r="R232" t="n">
-        <v>7090729</v>
+        <v>7090855</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24389,11 +24389,6 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24420,10 +24415,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128794454</v>
+        <v>128794446</v>
       </c>
       <c r="B233" t="n">
-        <v>80194</v>
+        <v>57716</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -24431,21 +24426,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24455,10 +24450,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>514732</v>
+        <v>514919</v>
       </c>
       <c r="R233" t="n">
-        <v>7090855</v>
+        <v>7090358</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24491,6 +24486,11 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -24520,7 +24520,7 @@
         <v>128794470</v>
       </c>
       <c r="B234" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>128794474</v>
       </c>
       <c r="B235" t="n">
-        <v>88867</v>
+        <v>88894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24716,10 +24716,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>128794457</v>
+        <v>128794459</v>
       </c>
       <c r="B236" t="n">
-        <v>56871</v>
+        <v>91512</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24727,46 +24727,34 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N236" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Renålandet S, Jmt</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>514546</v>
+        <v>514757</v>
       </c>
       <c r="R236" t="n">
-        <v>7090530</v>
+        <v>7090358</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24825,10 +24813,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>128794459</v>
+        <v>128794457</v>
       </c>
       <c r="B237" t="n">
-        <v>91485</v>
+        <v>56898</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24836,34 +24824,46 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Renålandet S, Jmt</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>514757</v>
+        <v>514546</v>
       </c>
       <c r="R237" t="n">
-        <v>7090358</v>
+        <v>7090530</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24925,7 +24925,7 @@
         <v>128794462</v>
       </c>
       <c r="B238" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>128794447</v>
       </c>
       <c r="B239" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>128794473</v>
       </c>
       <c r="B240" t="n">
-        <v>92041</v>
+        <v>92068</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -23627,7 +23627,7 @@
         <v>128794465</v>
       </c>
       <c r="B225" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23724,7 +23724,7 @@
         <v>128794471</v>
       </c>
       <c r="B226" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>128794452</v>
       </c>
       <c r="B227" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>128794466</v>
       </c>
       <c r="B228" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>128794451</v>
       </c>
       <c r="B229" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>128794468</v>
       </c>
       <c r="B230" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24219,7 +24219,7 @@
         <v>128794456</v>
       </c>
       <c r="B231" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>128794454</v>
       </c>
       <c r="B232" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>128794470</v>
       </c>
       <c r="B234" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>128794474</v>
       </c>
       <c r="B235" t="n">
-        <v>88894</v>
+        <v>88899</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>128794459</v>
       </c>
       <c r="B236" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>128794462</v>
       </c>
       <c r="B238" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>128794473</v>
       </c>
       <c r="B240" t="n">
-        <v>92068</v>
+        <v>92073</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -24119,10 +24119,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>128794446</v>
+        <v>128794456</v>
       </c>
       <c r="B230" t="n">
-        <v>57723</v>
+        <v>80139</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24130,21 +24130,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -24154,10 +24154,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>514919</v>
+        <v>514879</v>
       </c>
       <c r="R230" t="n">
-        <v>7090358</v>
+        <v>7090729</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24194,7 +24194,7 @@
       </c>
       <c r="AC230" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -24221,10 +24221,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128794468</v>
+        <v>128794454</v>
       </c>
       <c r="B231" t="n">
-        <v>91538</v>
+        <v>80139</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24232,21 +24232,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -24256,10 +24256,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>514537</v>
+        <v>514732</v>
       </c>
       <c r="R231" t="n">
-        <v>7090931</v>
+        <v>7090855</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24318,10 +24318,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128794456</v>
+        <v>128794446</v>
       </c>
       <c r="B232" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24329,21 +24329,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -24353,10 +24353,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>514879</v>
+        <v>514919</v>
       </c>
       <c r="R232" t="n">
-        <v>7090729</v>
+        <v>7090358</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="AC232" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24420,10 +24420,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128794454</v>
+        <v>128794468</v>
       </c>
       <c r="B233" t="n">
-        <v>80139</v>
+        <v>91538</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -24431,21 +24431,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24455,10 +24455,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>514732</v>
+        <v>514537</v>
       </c>
       <c r="R233" t="n">
-        <v>7090855</v>
+        <v>7090931</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24716,10 +24716,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>128794459</v>
+        <v>128794457</v>
       </c>
       <c r="B236" t="n">
-        <v>91538</v>
+        <v>56904</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24727,34 +24727,46 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Renålandet S, Jmt</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>514757</v>
+        <v>514546</v>
       </c>
       <c r="R236" t="n">
-        <v>7090358</v>
+        <v>7090530</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24813,10 +24825,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>128794457</v>
+        <v>128794459</v>
       </c>
       <c r="B237" t="n">
-        <v>56904</v>
+        <v>91538</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24824,46 +24836,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N237" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Renålandet S, Jmt</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>514546</v>
+        <v>514757</v>
       </c>
       <c r="R237" t="n">
-        <v>7090530</v>
+        <v>7090358</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -23624,10 +23624,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128794465</v>
+        <v>128794471</v>
       </c>
       <c r="B225" t="n">
-        <v>91538</v>
+        <v>79034</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23635,21 +23635,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23659,10 +23659,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>514919</v>
+        <v>514825</v>
       </c>
       <c r="R225" t="n">
-        <v>7090657</v>
+        <v>7090372</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23695,6 +23695,11 @@
       <c r="AA225" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -23721,10 +23726,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128794471</v>
+        <v>128794465</v>
       </c>
       <c r="B226" t="n">
-        <v>79034</v>
+        <v>91541</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23732,21 +23737,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23756,10 +23761,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>514825</v>
+        <v>514919</v>
       </c>
       <c r="R226" t="n">
-        <v>7090372</v>
+        <v>7090657</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23792,11 +23797,6 @@
       <c r="AA226" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24025,7 +24025,7 @@
         <v>128794466</v>
       </c>
       <c r="B229" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>128794468</v>
       </c>
       <c r="B233" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>128794474</v>
       </c>
       <c r="B235" t="n">
-        <v>88920</v>
+        <v>88923</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24716,10 +24716,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>128794457</v>
+        <v>128794459</v>
       </c>
       <c r="B236" t="n">
-        <v>56904</v>
+        <v>91541</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24727,46 +24727,34 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N236" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Renålandet S, Jmt</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>514546</v>
+        <v>514757</v>
       </c>
       <c r="R236" t="n">
-        <v>7090530</v>
+        <v>7090358</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24825,10 +24813,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>128794459</v>
+        <v>128794457</v>
       </c>
       <c r="B237" t="n">
-        <v>91538</v>
+        <v>56904</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24836,34 +24824,46 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Renålandet S, Jmt</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>514757</v>
+        <v>514546</v>
       </c>
       <c r="R237" t="n">
-        <v>7090358</v>
+        <v>7090530</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24925,7 +24925,7 @@
         <v>128794462</v>
       </c>
       <c r="B238" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>128794473</v>
       </c>
       <c r="B240" t="n">
-        <v>92095</v>
+        <v>92100</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY240"/>
+  <dimension ref="A1:AY253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23627,7 +23627,7 @@
         <v>128794471</v>
       </c>
       <c r="B225" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23729,7 +23729,7 @@
         <v>128794465</v>
       </c>
       <c r="B226" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>128794452</v>
       </c>
       <c r="B227" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>128794451</v>
       </c>
       <c r="B228" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -24025,7 +24025,7 @@
         <v>128794466</v>
       </c>
       <c r="B229" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>128794456</v>
       </c>
       <c r="B230" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>128794454</v>
       </c>
       <c r="B231" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24318,10 +24318,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128794446</v>
+        <v>128794468</v>
       </c>
       <c r="B232" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24329,21 +24329,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -24353,10 +24353,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>514919</v>
+        <v>514537</v>
       </c>
       <c r="R232" t="n">
-        <v>7090358</v>
+        <v>7090931</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24389,11 +24389,6 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24420,10 +24415,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128794468</v>
+        <v>128794446</v>
       </c>
       <c r="B233" t="n">
-        <v>91541</v>
+        <v>57723</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -24431,21 +24426,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24455,10 +24450,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>514537</v>
+        <v>514919</v>
       </c>
       <c r="R233" t="n">
-        <v>7090931</v>
+        <v>7090358</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24491,6 +24486,11 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -24520,7 +24520,7 @@
         <v>128794470</v>
       </c>
       <c r="B234" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>128794474</v>
       </c>
       <c r="B235" t="n">
-        <v>88923</v>
+        <v>88926</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24716,10 +24716,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>128794459</v>
+        <v>128794457</v>
       </c>
       <c r="B236" t="n">
-        <v>91541</v>
+        <v>56904</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24727,34 +24727,46 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Renålandet S, Jmt</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>514757</v>
+        <v>514546</v>
       </c>
       <c r="R236" t="n">
-        <v>7090358</v>
+        <v>7090530</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24813,10 +24825,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>128794457</v>
+        <v>128794459</v>
       </c>
       <c r="B237" t="n">
-        <v>56904</v>
+        <v>91544</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24824,46 +24836,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N237" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Renålandet S, Jmt</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>514546</v>
+        <v>514757</v>
       </c>
       <c r="R237" t="n">
-        <v>7090530</v>
+        <v>7090358</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24925,7 +24925,7 @@
         <v>128794462</v>
       </c>
       <c r="B238" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>128794473</v>
       </c>
       <c r="B240" t="n">
-        <v>92100</v>
+        <v>92103</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -25215,6 +25215,1320 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>129193606</v>
+      </c>
+      <c r="B241" t="n">
+        <v>91476</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>112</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr"/>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q241" t="n">
+        <v>514807</v>
+      </c>
+      <c r="R241" t="n">
+        <v>7090461</v>
+      </c>
+      <c r="S241" t="n">
+        <v>10</v>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD241" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE241" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG241" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT241" t="inlineStr"/>
+      <c r="AW241" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX241" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>129193598</v>
+      </c>
+      <c r="B242" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr"/>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q242" t="n">
+        <v>514293</v>
+      </c>
+      <c r="R242" t="n">
+        <v>7089925</v>
+      </c>
+      <c r="S242" t="n">
+        <v>10</v>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT242" t="inlineStr"/>
+      <c r="AW242" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX242" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>129193607</v>
+      </c>
+      <c r="B243" t="n">
+        <v>92231</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>67</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Sprickporing</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Diplomitoporus crustulinus</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr"/>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q243" t="n">
+        <v>514597</v>
+      </c>
+      <c r="R243" t="n">
+        <v>7090742</v>
+      </c>
+      <c r="S243" t="n">
+        <v>10</v>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT243" t="inlineStr"/>
+      <c r="AW243" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX243" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>129193603</v>
+      </c>
+      <c r="B244" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr"/>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q244" t="n">
+        <v>514034</v>
+      </c>
+      <c r="R244" t="n">
+        <v>7089971</v>
+      </c>
+      <c r="S244" t="n">
+        <v>10</v>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT244" t="inlineStr"/>
+      <c r="AW244" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX244" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>129193604</v>
+      </c>
+      <c r="B245" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr"/>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q245" t="n">
+        <v>514002</v>
+      </c>
+      <c r="R245" t="n">
+        <v>7090017</v>
+      </c>
+      <c r="S245" t="n">
+        <v>10</v>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT245" t="inlineStr"/>
+      <c r="AW245" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX245" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>129193599</v>
+      </c>
+      <c r="B246" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr"/>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q246" t="n">
+        <v>514083</v>
+      </c>
+      <c r="R246" t="n">
+        <v>7089840</v>
+      </c>
+      <c r="S246" t="n">
+        <v>10</v>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT246" t="inlineStr"/>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>129193600</v>
+      </c>
+      <c r="B247" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr"/>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q247" t="n">
+        <v>514067</v>
+      </c>
+      <c r="R247" t="n">
+        <v>7089887</v>
+      </c>
+      <c r="S247" t="n">
+        <v>10</v>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT247" t="inlineStr"/>
+      <c r="AW247" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX247" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>129193601</v>
+      </c>
+      <c r="B248" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr"/>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q248" t="n">
+        <v>514062</v>
+      </c>
+      <c r="R248" t="n">
+        <v>7089896</v>
+      </c>
+      <c r="S248" t="n">
+        <v>10</v>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT248" t="inlineStr"/>
+      <c r="AW248" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX248" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>129193608</v>
+      </c>
+      <c r="B249" t="n">
+        <v>91885</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr"/>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q249" t="n">
+        <v>514808</v>
+      </c>
+      <c r="R249" t="n">
+        <v>7090463</v>
+      </c>
+      <c r="S249" t="n">
+        <v>10</v>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD249" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE249" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG249" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT249" t="inlineStr"/>
+      <c r="AW249" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX249" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>129193602</v>
+      </c>
+      <c r="B250" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr"/>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q250" t="n">
+        <v>514066</v>
+      </c>
+      <c r="R250" t="n">
+        <v>7089974</v>
+      </c>
+      <c r="S250" t="n">
+        <v>10</v>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT250" t="inlineStr"/>
+      <c r="AW250" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX250" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>129193605</v>
+      </c>
+      <c r="B251" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr"/>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q251" t="n">
+        <v>513987</v>
+      </c>
+      <c r="R251" t="n">
+        <v>7090294</v>
+      </c>
+      <c r="S251" t="n">
+        <v>10</v>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT251" t="inlineStr"/>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>129193609</v>
+      </c>
+      <c r="B252" t="n">
+        <v>91811</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>658</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr"/>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q252" t="n">
+        <v>514242</v>
+      </c>
+      <c r="R252" t="n">
+        <v>7089880</v>
+      </c>
+      <c r="S252" t="n">
+        <v>10</v>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT252" t="inlineStr"/>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX252" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>129193597</v>
+      </c>
+      <c r="B253" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr"/>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr"/>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>Renålandet S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q253" t="n">
+        <v>514868</v>
+      </c>
+      <c r="R253" t="n">
+        <v>7090570</v>
+      </c>
+      <c r="S253" t="n">
+        <v>10</v>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>Möjligen tretå-bohål i asp, ca 3,5m upp.</t>
+        </is>
+      </c>
+      <c r="AD253" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE253" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG253" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT253" t="inlineStr"/>
+      <c r="AW253" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX253" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY253" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY253"/>
+  <dimension ref="A1:AY252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23624,10 +23624,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128794471</v>
+        <v>128794465</v>
       </c>
       <c r="B225" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23635,21 +23635,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23659,10 +23659,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>514825</v>
+        <v>514919</v>
       </c>
       <c r="R225" t="n">
-        <v>7090372</v>
+        <v>7090657</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23695,11 +23695,6 @@
       <c r="AA225" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC225" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -23726,10 +23721,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128794465</v>
+        <v>128794471</v>
       </c>
       <c r="B226" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23737,21 +23732,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23761,10 +23756,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>514919</v>
+        <v>514825</v>
       </c>
       <c r="R226" t="n">
-        <v>7090657</v>
+        <v>7090372</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23797,6 +23792,11 @@
       <c r="AA226" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -23920,10 +23920,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128794451</v>
+        <v>128794466</v>
       </c>
       <c r="B228" t="n">
-        <v>80140</v>
+        <v>91544</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -23931,21 +23931,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23955,10 +23955,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>514916</v>
+        <v>514904</v>
       </c>
       <c r="R228" t="n">
-        <v>7090603</v>
+        <v>7090715</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23991,11 +23991,6 @@
       <c r="AA228" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC228" t="inlineStr">
-        <is>
-          <t>På grangrenar</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -24022,10 +24017,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>128794466</v>
+        <v>128794451</v>
       </c>
       <c r="B229" t="n">
-        <v>91544</v>
+        <v>80140</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24033,21 +24028,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -24057,10 +24052,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>514904</v>
+        <v>514916</v>
       </c>
       <c r="R229" t="n">
-        <v>7090715</v>
+        <v>7090603</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24093,6 +24088,11 @@
       <c r="AA229" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>På grangrenar</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -24318,10 +24318,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128794468</v>
+        <v>128794446</v>
       </c>
       <c r="B232" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24329,21 +24329,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -24353,10 +24353,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>514537</v>
+        <v>514919</v>
       </c>
       <c r="R232" t="n">
-        <v>7090931</v>
+        <v>7090358</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24389,6 +24389,11 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24415,10 +24420,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128794446</v>
+        <v>128794468</v>
       </c>
       <c r="B233" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -24426,21 +24431,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24450,10 +24455,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>514919</v>
+        <v>514537</v>
       </c>
       <c r="R233" t="n">
-        <v>7090358</v>
+        <v>7090931</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24486,11 +24491,6 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -24716,10 +24716,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>128794457</v>
+        <v>128794459</v>
       </c>
       <c r="B236" t="n">
-        <v>56904</v>
+        <v>91544</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24727,46 +24727,34 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N236" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Renålandet S, Jmt</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>514546</v>
+        <v>514757</v>
       </c>
       <c r="R236" t="n">
-        <v>7090530</v>
+        <v>7090358</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24825,10 +24813,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>128794459</v>
+        <v>128794457</v>
       </c>
       <c r="B237" t="n">
-        <v>91544</v>
+        <v>56904</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24836,34 +24824,46 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Renålandet S, Jmt</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>514757</v>
+        <v>514546</v>
       </c>
       <c r="R237" t="n">
-        <v>7090358</v>
+        <v>7090530</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25315,32 +25315,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129193598</v>
+        <v>129193607</v>
       </c>
       <c r="B242" t="n">
-        <v>57723</v>
+        <v>92231</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -25350,10 +25350,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>514293</v>
+        <v>514597</v>
       </c>
       <c r="R242" t="n">
-        <v>7089925</v>
+        <v>7090742</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25386,11 +25386,6 @@
       <c r="AA242" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC242" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -25417,32 +25412,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129193607</v>
+        <v>129193598</v>
       </c>
       <c r="B243" t="n">
-        <v>92231</v>
+        <v>57723</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25452,10 +25447,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>514597</v>
+        <v>514293</v>
       </c>
       <c r="R243" t="n">
-        <v>7090742</v>
+        <v>7089925</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25488,6 +25483,11 @@
       <c r="AA243" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -26024,32 +26024,32 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>129193608</v>
+        <v>129193602</v>
       </c>
       <c r="B249" t="n">
-        <v>91885</v>
+        <v>57723</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -26059,10 +26059,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>514808</v>
+        <v>514066</v>
       </c>
       <c r="R249" t="n">
-        <v>7090463</v>
+        <v>7089974</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -26095,6 +26095,11 @@
       <c r="AA249" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -26121,7 +26126,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>129193602</v>
+        <v>129193605</v>
       </c>
       <c r="B250" t="n">
         <v>57723</v>
@@ -26156,10 +26161,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>514066</v>
+        <v>513987</v>
       </c>
       <c r="R250" t="n">
-        <v>7089974</v>
+        <v>7090294</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26196,7 +26201,7 @@
       </c>
       <c r="AC250" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -26223,10 +26228,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>129193605</v>
+        <v>129193609</v>
       </c>
       <c r="B251" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26234,21 +26239,21 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -26258,10 +26263,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>513987</v>
+        <v>514242</v>
       </c>
       <c r="R251" t="n">
-        <v>7090294</v>
+        <v>7089880</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26294,11 +26299,6 @@
       <c r="AA251" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -26325,10 +26325,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>129193609</v>
+        <v>129193597</v>
       </c>
       <c r="B252" t="n">
-        <v>91811</v>
+        <v>57723</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -26336,34 +26336,42 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
           <t>Renålandet S, Jmt</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>514242</v>
+        <v>514868</v>
       </c>
       <c r="R252" t="n">
-        <v>7089880</v>
+        <v>7090570</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26398,6 +26406,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>Möjligen tretå-bohål i asp, ca 3,5m upp.</t>
+        </is>
+      </c>
       <c r="AD252" t="b">
         <v>0</v>
       </c>
@@ -26419,116 +26432,6 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
-    </row>
-    <row r="253">
-      <c r="A253" t="n">
-        <v>129193597</v>
-      </c>
-      <c r="B253" t="n">
-        <v>57723</v>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E253" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I253" t="inlineStr"/>
-      <c r="K253" t="inlineStr"/>
-      <c r="L253" t="inlineStr"/>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N253" t="inlineStr"/>
-      <c r="P253" t="inlineStr">
-        <is>
-          <t>Renålandet S, Jmt</t>
-        </is>
-      </c>
-      <c r="Q253" t="n">
-        <v>514868</v>
-      </c>
-      <c r="R253" t="n">
-        <v>7090570</v>
-      </c>
-      <c r="S253" t="n">
-        <v>10</v>
-      </c>
-      <c r="T253" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U253" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V253" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W253" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y253" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AA253" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>Möjligen tretå-bohål i asp, ca 3,5m upp.</t>
-        </is>
-      </c>
-      <c r="AD253" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE253" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG253" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT253" t="inlineStr"/>
-      <c r="AW253" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX253" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY253" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -24119,10 +24119,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>128794456</v>
+        <v>128794468</v>
       </c>
       <c r="B230" t="n">
-        <v>80140</v>
+        <v>91544</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24130,21 +24130,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -24154,10 +24154,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>514879</v>
+        <v>514537</v>
       </c>
       <c r="R230" t="n">
-        <v>7090729</v>
+        <v>7090931</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24190,11 +24190,6 @@
       <c r="AA230" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -24221,7 +24216,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128794454</v>
+        <v>128794456</v>
       </c>
       <c r="B231" t="n">
         <v>80140</v>
@@ -24256,10 +24251,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>514732</v>
+        <v>514879</v>
       </c>
       <c r="R231" t="n">
-        <v>7090855</v>
+        <v>7090729</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24292,6 +24287,11 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24318,10 +24318,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128794446</v>
+        <v>128794454</v>
       </c>
       <c r="B232" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24329,21 +24329,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -24353,10 +24353,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>514919</v>
+        <v>514732</v>
       </c>
       <c r="R232" t="n">
-        <v>7090358</v>
+        <v>7090855</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24389,11 +24389,6 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24420,10 +24415,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128794468</v>
+        <v>128794446</v>
       </c>
       <c r="B233" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -24431,21 +24426,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24455,10 +24450,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>514537</v>
+        <v>514919</v>
       </c>
       <c r="R233" t="n">
-        <v>7090931</v>
+        <v>7090358</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24491,6 +24486,11 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD233" t="b">

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -24716,10 +24716,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>128794459</v>
+        <v>128794457</v>
       </c>
       <c r="B236" t="n">
-        <v>91544</v>
+        <v>56904</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24727,34 +24727,46 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Renålandet S, Jmt</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>514757</v>
+        <v>514546</v>
       </c>
       <c r="R236" t="n">
-        <v>7090358</v>
+        <v>7090530</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24813,10 +24825,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>128794457</v>
+        <v>128794459</v>
       </c>
       <c r="B237" t="n">
-        <v>56904</v>
+        <v>91544</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24824,46 +24836,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N237" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Renålandet S, Jmt</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>514546</v>
+        <v>514757</v>
       </c>
       <c r="R237" t="n">
-        <v>7090530</v>
+        <v>7090358</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -23627,7 +23627,7 @@
         <v>128794465</v>
       </c>
       <c r="B225" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23724,7 +23724,7 @@
         <v>128794471</v>
       </c>
       <c r="B226" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>128794452</v>
       </c>
       <c r="B227" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>128794466</v>
       </c>
       <c r="B228" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>128794451</v>
       </c>
       <c r="B229" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>128794468</v>
       </c>
       <c r="B230" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24216,10 +24216,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128794456</v>
+        <v>128794446</v>
       </c>
       <c r="B231" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24227,21 +24227,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -24251,10 +24251,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>514879</v>
+        <v>514919</v>
       </c>
       <c r="R231" t="n">
-        <v>7090729</v>
+        <v>7090358</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24291,7 +24291,7 @@
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24318,10 +24318,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128794454</v>
+        <v>128794456</v>
       </c>
       <c r="B232" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24353,10 +24353,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>514732</v>
+        <v>514879</v>
       </c>
       <c r="R232" t="n">
-        <v>7090855</v>
+        <v>7090729</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24389,6 +24389,11 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24415,10 +24420,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128794446</v>
+        <v>128794454</v>
       </c>
       <c r="B233" t="n">
-        <v>57723</v>
+        <v>80144</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -24426,21 +24431,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24450,10 +24455,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>514919</v>
+        <v>514732</v>
       </c>
       <c r="R233" t="n">
-        <v>7090358</v>
+        <v>7090855</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24486,11 +24491,6 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -24520,7 +24520,7 @@
         <v>128794470</v>
       </c>
       <c r="B234" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>128794474</v>
       </c>
       <c r="B235" t="n">
-        <v>88926</v>
+        <v>88930</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>128794457</v>
       </c>
       <c r="B236" t="n">
-        <v>56904</v>
+        <v>56906</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>128794459</v>
       </c>
       <c r="B237" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>128794462</v>
       </c>
       <c r="B238" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>128794447</v>
       </c>
       <c r="B239" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>128794473</v>
       </c>
       <c r="B240" t="n">
-        <v>92103</v>
+        <v>92110</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>129193606</v>
       </c>
       <c r="B241" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -25315,32 +25315,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129193607</v>
+        <v>129193598</v>
       </c>
       <c r="B242" t="n">
-        <v>92231</v>
+        <v>57725</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -25350,10 +25350,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>514597</v>
+        <v>514293</v>
       </c>
       <c r="R242" t="n">
-        <v>7090742</v>
+        <v>7089925</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25386,6 +25386,11 @@
       <c r="AA242" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -25412,32 +25417,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129193598</v>
+        <v>129193607</v>
       </c>
       <c r="B243" t="n">
-        <v>57723</v>
+        <v>92238</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25447,10 +25452,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>514293</v>
+        <v>514597</v>
       </c>
       <c r="R243" t="n">
-        <v>7089925</v>
+        <v>7090742</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25483,11 +25488,6 @@
       <c r="AA243" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC243" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -25517,7 +25517,7 @@
         <v>129193603</v>
       </c>
       <c r="B244" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>129193604</v>
       </c>
       <c r="B245" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>129193599</v>
       </c>
       <c r="B246" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>129193600</v>
       </c>
       <c r="B247" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>129193601</v>
       </c>
       <c r="B248" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>129193602</v>
       </c>
       <c r="B249" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>129193605</v>
       </c>
       <c r="B250" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>129193609</v>
       </c>
       <c r="B251" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>129193597</v>
       </c>
       <c r="B252" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -24216,10 +24216,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128794446</v>
+        <v>128794456</v>
       </c>
       <c r="B231" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24227,21 +24227,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -24251,10 +24251,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>514919</v>
+        <v>514879</v>
       </c>
       <c r="R231" t="n">
-        <v>7090358</v>
+        <v>7090729</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24291,7 +24291,7 @@
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24318,7 +24318,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128794456</v>
+        <v>128794454</v>
       </c>
       <c r="B232" t="n">
         <v>80144</v>
@@ -24353,10 +24353,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>514879</v>
+        <v>514732</v>
       </c>
       <c r="R232" t="n">
-        <v>7090729</v>
+        <v>7090855</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24389,11 +24389,6 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24420,10 +24415,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128794454</v>
+        <v>128794446</v>
       </c>
       <c r="B233" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -24431,21 +24426,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24455,10 +24450,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>514732</v>
+        <v>514919</v>
       </c>
       <c r="R233" t="n">
-        <v>7090855</v>
+        <v>7090358</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24491,6 +24486,11 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD233" t="b">

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -23627,7 +23627,7 @@
         <v>128794465</v>
       </c>
       <c r="B225" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>128794466</v>
       </c>
       <c r="B228" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>128794468</v>
       </c>
       <c r="B230" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128794456</v>
+        <v>128794454</v>
       </c>
       <c r="B231" t="n">
         <v>80144</v>
@@ -24251,10 +24251,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>514879</v>
+        <v>514732</v>
       </c>
       <c r="R231" t="n">
-        <v>7090729</v>
+        <v>7090855</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24287,11 +24287,6 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24318,7 +24313,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128794454</v>
+        <v>128794456</v>
       </c>
       <c r="B232" t="n">
         <v>80144</v>
@@ -24353,10 +24348,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>514732</v>
+        <v>514879</v>
       </c>
       <c r="R232" t="n">
-        <v>7090855</v>
+        <v>7090729</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24389,6 +24384,11 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24622,7 +24622,7 @@
         <v>128794474</v>
       </c>
       <c r="B235" t="n">
-        <v>88930</v>
+        <v>88937</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24716,10 +24716,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>128794457</v>
+        <v>128794459</v>
       </c>
       <c r="B236" t="n">
-        <v>56906</v>
+        <v>91558</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24727,46 +24727,34 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N236" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Renålandet S, Jmt</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>514546</v>
+        <v>514757</v>
       </c>
       <c r="R236" t="n">
-        <v>7090530</v>
+        <v>7090358</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24825,10 +24813,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>128794459</v>
+        <v>128794457</v>
       </c>
       <c r="B237" t="n">
-        <v>91551</v>
+        <v>56906</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24836,34 +24824,46 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Renålandet S, Jmt</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>514757</v>
+        <v>514546</v>
       </c>
       <c r="R237" t="n">
-        <v>7090358</v>
+        <v>7090530</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24925,7 +24925,7 @@
         <v>128794462</v>
       </c>
       <c r="B238" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>128794473</v>
       </c>
       <c r="B240" t="n">
-        <v>92110</v>
+        <v>92117</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>129193606</v>
       </c>
       <c r="B241" t="n">
-        <v>91482</v>
+        <v>91489</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -25315,32 +25315,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129193598</v>
+        <v>129193607</v>
       </c>
       <c r="B242" t="n">
-        <v>57725</v>
+        <v>92245</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -25350,10 +25350,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>514293</v>
+        <v>514597</v>
       </c>
       <c r="R242" t="n">
-        <v>7089925</v>
+        <v>7090742</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25386,11 +25386,6 @@
       <c r="AA242" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC242" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -25417,32 +25412,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129193607</v>
+        <v>129193598</v>
       </c>
       <c r="B243" t="n">
-        <v>92238</v>
+        <v>57725</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25452,10 +25447,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>514597</v>
+        <v>514293</v>
       </c>
       <c r="R243" t="n">
-        <v>7090742</v>
+        <v>7089925</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25488,6 +25483,11 @@
       <c r="AA243" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -26231,7 +26231,7 @@
         <v>129193609</v>
       </c>
       <c r="B251" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -23624,10 +23624,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128794465</v>
+        <v>128794471</v>
       </c>
       <c r="B225" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23635,21 +23635,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23659,10 +23659,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>514919</v>
+        <v>514825</v>
       </c>
       <c r="R225" t="n">
-        <v>7090657</v>
+        <v>7090372</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23695,6 +23695,11 @@
       <c r="AA225" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -23721,10 +23726,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128794471</v>
+        <v>128794465</v>
       </c>
       <c r="B226" t="n">
-        <v>79039</v>
+        <v>91560</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23732,21 +23737,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23756,10 +23761,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>514825</v>
+        <v>514919</v>
       </c>
       <c r="R226" t="n">
-        <v>7090372</v>
+        <v>7090657</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23792,11 +23797,6 @@
       <c r="AA226" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -23826,7 +23826,7 @@
         <v>128794452</v>
       </c>
       <c r="B227" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>128794466</v>
       </c>
       <c r="B228" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>128794451</v>
       </c>
       <c r="B229" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>128794468</v>
       </c>
       <c r="B230" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24216,10 +24216,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128794454</v>
+        <v>128794456</v>
       </c>
       <c r="B231" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24251,10 +24251,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>514732</v>
+        <v>514879</v>
       </c>
       <c r="R231" t="n">
-        <v>7090855</v>
+        <v>7090729</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24287,6 +24287,11 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24313,10 +24318,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128794456</v>
+        <v>128794454</v>
       </c>
       <c r="B232" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24348,10 +24353,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>514879</v>
+        <v>514732</v>
       </c>
       <c r="R232" t="n">
-        <v>7090729</v>
+        <v>7090855</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24384,11 +24389,6 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24418,7 +24418,7 @@
         <v>128794446</v>
       </c>
       <c r="B233" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>128794470</v>
       </c>
       <c r="B234" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>128794474</v>
       </c>
       <c r="B235" t="n">
-        <v>88937</v>
+        <v>88939</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>128794459</v>
       </c>
       <c r="B236" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>128794457</v>
       </c>
       <c r="B237" t="n">
-        <v>56906</v>
+        <v>56908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>128794462</v>
       </c>
       <c r="B238" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>128794447</v>
       </c>
       <c r="B239" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>128794473</v>
       </c>
       <c r="B240" t="n">
-        <v>92117</v>
+        <v>92119</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>129193606</v>
       </c>
       <c r="B241" t="n">
-        <v>91489</v>
+        <v>91491</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>129193607</v>
       </c>
       <c r="B242" t="n">
-        <v>92245</v>
+        <v>92247</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -25415,7 +25415,7 @@
         <v>129193598</v>
       </c>
       <c r="B243" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         <v>129193603</v>
       </c>
       <c r="B244" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>129193604</v>
       </c>
       <c r="B245" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>129193599</v>
       </c>
       <c r="B246" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>129193600</v>
       </c>
       <c r="B247" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>129193601</v>
       </c>
       <c r="B248" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>129193602</v>
       </c>
       <c r="B249" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>129193605</v>
       </c>
       <c r="B250" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>129193609</v>
       </c>
       <c r="B251" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>129193597</v>
       </c>
       <c r="B252" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -24119,10 +24119,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>128794468</v>
+        <v>128794456</v>
       </c>
       <c r="B230" t="n">
-        <v>91560</v>
+        <v>80146</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24130,21 +24130,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -24154,10 +24154,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>514537</v>
+        <v>514879</v>
       </c>
       <c r="R230" t="n">
-        <v>7090931</v>
+        <v>7090729</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24190,6 +24190,11 @@
       <c r="AA230" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -24216,7 +24221,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128794456</v>
+        <v>128794454</v>
       </c>
       <c r="B231" t="n">
         <v>80146</v>
@@ -24251,10 +24256,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>514879</v>
+        <v>514732</v>
       </c>
       <c r="R231" t="n">
-        <v>7090729</v>
+        <v>7090855</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24287,11 +24292,6 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24318,10 +24318,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128794454</v>
+        <v>128794446</v>
       </c>
       <c r="B232" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24329,21 +24329,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -24353,10 +24353,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>514732</v>
+        <v>514919</v>
       </c>
       <c r="R232" t="n">
-        <v>7090855</v>
+        <v>7090358</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24389,6 +24389,11 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24415,10 +24420,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128794446</v>
+        <v>128794468</v>
       </c>
       <c r="B233" t="n">
-        <v>57727</v>
+        <v>91560</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -24426,21 +24431,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24450,10 +24455,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>514919</v>
+        <v>514537</v>
       </c>
       <c r="R233" t="n">
-        <v>7090358</v>
+        <v>7090931</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24486,11 +24491,6 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -24716,10 +24716,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>128794459</v>
+        <v>128794457</v>
       </c>
       <c r="B236" t="n">
-        <v>91560</v>
+        <v>56908</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24727,34 +24727,46 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Renålandet S, Jmt</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>514757</v>
+        <v>514546</v>
       </c>
       <c r="R236" t="n">
-        <v>7090358</v>
+        <v>7090530</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24813,10 +24825,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>128794457</v>
+        <v>128794459</v>
       </c>
       <c r="B237" t="n">
-        <v>56908</v>
+        <v>91560</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24824,46 +24836,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N237" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Renålandet S, Jmt</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>514546</v>
+        <v>514757</v>
       </c>
       <c r="R237" t="n">
-        <v>7090530</v>
+        <v>7090358</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -24119,10 +24119,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>128794456</v>
+        <v>128794468</v>
       </c>
       <c r="B230" t="n">
-        <v>80146</v>
+        <v>91560</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24130,21 +24130,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -24154,10 +24154,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>514879</v>
+        <v>514537</v>
       </c>
       <c r="R230" t="n">
-        <v>7090729</v>
+        <v>7090931</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24190,11 +24190,6 @@
       <c r="AA230" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -24221,7 +24216,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128794454</v>
+        <v>128794456</v>
       </c>
       <c r="B231" t="n">
         <v>80146</v>
@@ -24256,10 +24251,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>514732</v>
+        <v>514879</v>
       </c>
       <c r="R231" t="n">
-        <v>7090855</v>
+        <v>7090729</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24292,6 +24287,11 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24318,10 +24318,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128794446</v>
+        <v>128794454</v>
       </c>
       <c r="B232" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24329,21 +24329,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -24353,10 +24353,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>514919</v>
+        <v>514732</v>
       </c>
       <c r="R232" t="n">
-        <v>7090358</v>
+        <v>7090855</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24389,11 +24389,6 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24420,10 +24415,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128794468</v>
+        <v>128794446</v>
       </c>
       <c r="B233" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -24431,21 +24426,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24455,10 +24450,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>514537</v>
+        <v>514919</v>
       </c>
       <c r="R233" t="n">
-        <v>7090931</v>
+        <v>7090358</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24491,6 +24486,11 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -24716,10 +24716,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>128794457</v>
+        <v>128794459</v>
       </c>
       <c r="B236" t="n">
-        <v>56908</v>
+        <v>91560</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24727,46 +24727,34 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N236" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Renålandet S, Jmt</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>514546</v>
+        <v>514757</v>
       </c>
       <c r="R236" t="n">
-        <v>7090530</v>
+        <v>7090358</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24825,10 +24813,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>128794459</v>
+        <v>128794457</v>
       </c>
       <c r="B237" t="n">
-        <v>91560</v>
+        <v>56908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24836,34 +24824,46 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Renålandet S, Jmt</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>514757</v>
+        <v>514546</v>
       </c>
       <c r="R237" t="n">
-        <v>7090358</v>
+        <v>7090530</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -23729,7 +23729,7 @@
         <v>128794465</v>
       </c>
       <c r="B226" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>128794466</v>
       </c>
       <c r="B228" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>128794468</v>
       </c>
       <c r="B230" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24216,10 +24216,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128794456</v>
+        <v>128794446</v>
       </c>
       <c r="B231" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24227,21 +24227,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -24251,10 +24251,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>514879</v>
+        <v>514919</v>
       </c>
       <c r="R231" t="n">
-        <v>7090729</v>
+        <v>7090358</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24291,7 +24291,7 @@
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24318,7 +24318,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128794454</v>
+        <v>128794456</v>
       </c>
       <c r="B232" t="n">
         <v>80146</v>
@@ -24353,10 +24353,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>514732</v>
+        <v>514879</v>
       </c>
       <c r="R232" t="n">
-        <v>7090855</v>
+        <v>7090729</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24389,6 +24389,11 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24415,10 +24420,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128794446</v>
+        <v>128794454</v>
       </c>
       <c r="B233" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -24426,21 +24431,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24450,10 +24455,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>514919</v>
+        <v>514732</v>
       </c>
       <c r="R233" t="n">
-        <v>7090358</v>
+        <v>7090855</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24486,11 +24491,6 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -24622,7 +24622,7 @@
         <v>128794474</v>
       </c>
       <c r="B235" t="n">
-        <v>88939</v>
+        <v>88940</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>128794459</v>
       </c>
       <c r="B236" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>128794462</v>
       </c>
       <c r="B238" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>128794473</v>
       </c>
       <c r="B240" t="n">
-        <v>92119</v>
+        <v>92134</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>129193607</v>
       </c>
       <c r="B242" t="n">
-        <v>92247</v>
+        <v>92262</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>129193609</v>
       </c>
       <c r="B251" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -25318,7 +25318,7 @@
         <v>129193607</v>
       </c>
       <c r="B242" t="n">
-        <v>92262</v>
+        <v>92263</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>129193609</v>
       </c>
       <c r="B251" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -25221,7 +25221,7 @@
         <v>129193606</v>
       </c>
       <c r="B241" t="n">
-        <v>91491</v>
+        <v>91494</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>129193607</v>
       </c>
       <c r="B242" t="n">
-        <v>92263</v>
+        <v>92266</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>129193609</v>
       </c>
       <c r="B251" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -25221,7 +25221,7 @@
         <v>129193606</v>
       </c>
       <c r="B241" t="n">
-        <v>91494</v>
+        <v>91496</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>129193607</v>
       </c>
       <c r="B242" t="n">
-        <v>92266</v>
+        <v>92268</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>129193609</v>
       </c>
       <c r="B251" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -25221,7 +25221,7 @@
         <v>129193606</v>
       </c>
       <c r="B241" t="n">
-        <v>91496</v>
+        <v>91500</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -25315,32 +25315,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129193607</v>
+        <v>129193598</v>
       </c>
       <c r="B242" t="n">
-        <v>92268</v>
+        <v>57727</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -25350,10 +25350,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>514597</v>
+        <v>514293</v>
       </c>
       <c r="R242" t="n">
-        <v>7090742</v>
+        <v>7089925</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25386,6 +25386,11 @@
       <c r="AA242" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -25412,32 +25417,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129193598</v>
+        <v>129193607</v>
       </c>
       <c r="B243" t="n">
-        <v>57727</v>
+        <v>92272</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25447,10 +25452,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>514293</v>
+        <v>514597</v>
       </c>
       <c r="R243" t="n">
-        <v>7089925</v>
+        <v>7090742</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25483,11 +25488,6 @@
       <c r="AA243" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC243" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -26231,7 +26231,7 @@
         <v>129193609</v>
       </c>
       <c r="B251" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -25221,7 +25221,7 @@
         <v>129193606</v>
       </c>
       <c r="B241" t="n">
-        <v>91500</v>
+        <v>91501</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -25315,32 +25315,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129193598</v>
+        <v>129193607</v>
       </c>
       <c r="B242" t="n">
-        <v>57727</v>
+        <v>92273</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -25350,10 +25350,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>514293</v>
+        <v>514597</v>
       </c>
       <c r="R242" t="n">
-        <v>7089925</v>
+        <v>7090742</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25386,11 +25386,6 @@
       <c r="AA242" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC242" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -25417,32 +25412,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129193607</v>
+        <v>129193598</v>
       </c>
       <c r="B243" t="n">
-        <v>92272</v>
+        <v>57727</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25452,10 +25447,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>514597</v>
+        <v>514293</v>
       </c>
       <c r="R243" t="n">
-        <v>7090742</v>
+        <v>7089925</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25488,6 +25483,11 @@
       <c r="AA243" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -26231,7 +26231,7 @@
         <v>129193609</v>
       </c>
       <c r="B251" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -25221,7 +25221,7 @@
         <v>129193606</v>
       </c>
       <c r="B241" t="n">
-        <v>91501</v>
+        <v>91504</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>129193607</v>
       </c>
       <c r="B242" t="n">
-        <v>92273</v>
+        <v>92276</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>129193609</v>
       </c>
       <c r="B251" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -25221,7 +25221,7 @@
         <v>129193606</v>
       </c>
       <c r="B241" t="n">
-        <v>91504</v>
+        <v>91532</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -25315,32 +25315,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129193607</v>
+        <v>129193598</v>
       </c>
       <c r="B242" t="n">
-        <v>92276</v>
+        <v>57730</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -25350,10 +25350,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>514597</v>
+        <v>514293</v>
       </c>
       <c r="R242" t="n">
-        <v>7090742</v>
+        <v>7089925</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25386,6 +25386,11 @@
       <c r="AA242" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -25412,32 +25417,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129193598</v>
+        <v>129193607</v>
       </c>
       <c r="B243" t="n">
-        <v>57727</v>
+        <v>92304</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25447,10 +25452,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>514293</v>
+        <v>514597</v>
       </c>
       <c r="R243" t="n">
-        <v>7089925</v>
+        <v>7090742</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25483,11 +25488,6 @@
       <c r="AA243" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC243" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -25517,7 +25517,7 @@
         <v>129193603</v>
       </c>
       <c r="B244" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>129193604</v>
       </c>
       <c r="B245" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>129193599</v>
       </c>
       <c r="B246" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>129193600</v>
       </c>
       <c r="B247" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>129193601</v>
       </c>
       <c r="B248" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>129193602</v>
       </c>
       <c r="B249" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>129193605</v>
       </c>
       <c r="B250" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>129193609</v>
       </c>
       <c r="B251" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>129193597</v>
       </c>
       <c r="B252" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -25315,32 +25315,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129193598</v>
+        <v>129193607</v>
       </c>
       <c r="B242" t="n">
-        <v>57730</v>
+        <v>92304</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -25350,10 +25350,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>514293</v>
+        <v>514597</v>
       </c>
       <c r="R242" t="n">
-        <v>7089925</v>
+        <v>7090742</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25386,11 +25386,6 @@
       <c r="AA242" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC242" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -25417,32 +25412,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129193607</v>
+        <v>129193598</v>
       </c>
       <c r="B243" t="n">
-        <v>92304</v>
+        <v>57730</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25452,10 +25447,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>514597</v>
+        <v>514293</v>
       </c>
       <c r="R243" t="n">
-        <v>7090742</v>
+        <v>7089925</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25488,6 +25483,11 @@
       <c r="AA243" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD243" t="b">

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -25415,7 +25415,7 @@
         <v>129193598</v>
       </c>
       <c r="B243" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         <v>129193603</v>
       </c>
       <c r="B244" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>129193604</v>
       </c>
       <c r="B245" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>129193599</v>
       </c>
       <c r="B246" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>129193600</v>
       </c>
       <c r="B247" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>129193601</v>
       </c>
       <c r="B248" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>129193602</v>
       </c>
       <c r="B249" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>129193605</v>
       </c>
       <c r="B250" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>129193597</v>
       </c>
       <c r="B252" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -25415,7 +25415,7 @@
         <v>129193598</v>
       </c>
       <c r="B243" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         <v>129193603</v>
       </c>
       <c r="B244" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>129193604</v>
       </c>
       <c r="B245" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>129193599</v>
       </c>
       <c r="B246" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>129193600</v>
       </c>
       <c r="B247" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>129193601</v>
       </c>
       <c r="B248" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>129193602</v>
       </c>
       <c r="B249" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>129193605</v>
       </c>
       <c r="B250" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>129193597</v>
       </c>
       <c r="B252" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -25415,7 +25415,7 @@
         <v>129193598</v>
       </c>
       <c r="B243" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         <v>129193603</v>
       </c>
       <c r="B244" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>129193604</v>
       </c>
       <c r="B245" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>129193599</v>
       </c>
       <c r="B246" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>129193600</v>
       </c>
       <c r="B247" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>129193601</v>
       </c>
       <c r="B248" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>129193602</v>
       </c>
       <c r="B249" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>129193605</v>
       </c>
       <c r="B250" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>129193597</v>
       </c>
       <c r="B252" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -25415,7 +25415,7 @@
         <v>129193598</v>
       </c>
       <c r="B243" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         <v>129193603</v>
       </c>
       <c r="B244" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>129193604</v>
       </c>
       <c r="B245" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>129193599</v>
       </c>
       <c r="B246" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>129193600</v>
       </c>
       <c r="B247" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>129193601</v>
       </c>
       <c r="B248" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>129193602</v>
       </c>
       <c r="B249" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>129193605</v>
       </c>
       <c r="B250" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>129193597</v>
       </c>
       <c r="B252" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 37713-2025 artfynd.xlsx
+++ b/artfynd/A 37713-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY257"/>
+  <dimension ref="A1:AZ257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118975310</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086263</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297794</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193607</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086282</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193606</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086321</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118973289</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086316</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794474</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1769,6 +1824,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118968866</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1866,6 +1926,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193609</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1963,6 +2028,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794473</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2060,6 +2130,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119085831</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2157,6 +2232,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086269</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2254,6 +2334,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086270</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2351,6 +2436,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086271</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2448,6 +2538,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086272</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2545,6 +2640,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119349142</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2642,6 +2742,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119349143</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2739,6 +2844,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086308</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2836,6 +2946,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086309</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2933,6 +3048,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086310</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3030,6 +3150,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086311</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3127,6 +3252,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086280</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3224,6 +3354,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297554</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3321,6 +3456,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086267</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3418,6 +3558,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086268</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3515,6 +3660,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086292</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3612,6 +3762,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086294</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3709,6 +3864,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086295</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3806,6 +3966,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119085854</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3903,6 +4068,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086289</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4000,6 +4170,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119261471</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4097,6 +4272,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119261472</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4194,6 +4374,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119268035</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4291,6 +4476,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297539</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4388,6 +4578,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297540</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4485,6 +4680,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297541</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4582,6 +4782,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297829</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4679,6 +4884,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086304</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4776,6 +4986,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297796</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4873,6 +5088,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297553</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4970,6 +5190,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086323</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5067,6 +5292,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086317</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5164,6 +5394,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297609</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5261,6 +5496,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297610</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5358,6 +5598,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297542</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5455,6 +5700,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297795</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5552,6 +5802,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086313</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5649,6 +5904,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297577</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5746,6 +6006,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297578</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5843,6 +6108,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297579</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5940,6 +6210,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297580</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6037,6 +6312,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297581</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6134,6 +6414,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297582</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6231,6 +6516,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297583</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6328,6 +6618,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297584</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6425,6 +6720,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297585</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6522,6 +6822,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297586</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6619,6 +6924,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297587</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6716,6 +7026,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297588</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6813,6 +7128,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297589</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6910,6 +7230,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297590</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7007,6 +7332,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297591</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7104,6 +7434,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297592</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7201,6 +7536,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297594</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7298,6 +7638,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297595</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7395,6 +7740,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297597</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7492,6 +7842,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297598</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7589,6 +7944,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297599</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7686,6 +8046,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297601</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7783,6 +8148,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297602</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7880,6 +8250,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297603</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7977,6 +8352,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297604</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8074,6 +8454,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297605</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8171,6 +8556,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297606</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8268,6 +8658,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297607</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8365,6 +8760,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297608</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8462,6 +8862,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119349202</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8564,6 +8969,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794470</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8666,6 +9076,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794471</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8763,6 +9178,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086307</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8860,6 +9280,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119268004</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8957,6 +9382,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297519</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9054,6 +9484,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297520</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9151,6 +9586,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297521</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9248,6 +9688,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297522</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9346,6 +9791,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297523</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9444,6 +9894,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297524</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9542,6 +9997,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119349127</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9639,6 +10099,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086288</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9746,6 +10211,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118973482</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9843,6 +10313,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297575</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9955,6 +10430,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118973492</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10052,6 +10532,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086264</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10149,6 +10634,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086265</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10246,6 +10736,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086290</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10343,6 +10838,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086296</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10440,6 +10940,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086297</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10537,6 +11042,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086300</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10634,6 +11144,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119261517</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10731,6 +11246,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119261518</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10828,6 +11348,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119261519</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10944,6 +11469,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119268040</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11041,6 +11571,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119268041</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11138,6 +11673,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119268042</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11235,6 +11775,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119268069</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11332,6 +11877,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119268070</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11429,6 +11979,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119268071</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11526,6 +12081,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119268072</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11623,6 +12183,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119268073</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11720,6 +12285,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119268074</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11817,6 +12387,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119268075</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11914,6 +12489,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297556</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12011,6 +12591,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297557</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12108,6 +12693,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297558</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12205,6 +12795,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297559</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12302,6 +12897,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297561</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12399,6 +12999,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297562</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12496,6 +13101,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297563</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12593,6 +13203,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297564</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12690,6 +13305,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297565</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12787,6 +13407,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297566</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12884,6 +13509,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297567</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -12981,6 +13611,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297568</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13078,6 +13713,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297824</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13175,6 +13815,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297825</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13272,6 +13917,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297826</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13369,6 +14019,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297827</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13482,6 +14137,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119349166</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13585,6 +14245,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119349167</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13703,6 +14368,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119349168</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13800,6 +14470,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119349170</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13897,6 +14572,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119349171</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -13994,6 +14674,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119349172</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14091,6 +14776,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119349173</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14188,6 +14878,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119349174</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14285,6 +14980,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119349175</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14401,6 +15101,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120061015</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14498,6 +15203,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120061029</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14595,6 +15305,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120061030</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14696,6 +15411,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120061032</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14798,6 +15518,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794451</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -14895,6 +15620,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794452</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -14992,6 +15722,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794454</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15094,6 +15829,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794456</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15191,6 +15931,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297823</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15288,6 +16033,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086278</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15385,6 +16135,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086279</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15482,6 +16237,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119261461</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15579,6 +16339,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119261462</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15676,6 +16441,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119268020</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15773,6 +16543,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297527</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -15870,6 +16645,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297528</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -15967,6 +16747,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297529</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16064,6 +16849,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297530</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16161,6 +16951,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297532</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16258,6 +17053,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297533</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16355,6 +17155,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297798</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16452,6 +17257,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119349150</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16559,6 +17369,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118974032</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16656,6 +17471,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086319</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -16753,6 +17573,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086320</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -16850,6 +17675,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086302</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -16947,6 +17777,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086303</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17044,6 +17879,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119261523</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17141,6 +17981,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119261524</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17238,6 +18083,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119268077</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17335,6 +18185,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119268078</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17432,6 +18287,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119268079</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -17529,6 +18389,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297569</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -17626,6 +18491,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297570</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -17723,6 +18593,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297571</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -17820,6 +18695,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297573</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -17917,6 +18797,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119349176</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18014,6 +18899,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086286</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18111,6 +19001,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119261467</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18213,6 +19108,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086273</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18315,6 +19215,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794446</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18417,6 +19322,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794447</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -18527,6 +19437,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193597</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -18629,6 +19544,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193598</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -18731,6 +19651,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193599</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -18833,6 +19758,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193600</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -18935,6 +19865,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193601</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -19037,6 +19972,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193602</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19139,6 +20079,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193603</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19241,6 +20186,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193604</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19343,6 +20293,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193605</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19440,6 +20395,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297526</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -19549,6 +20509,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794457</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -19646,6 +20611,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119349149</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -19743,6 +20713,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119349177</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -19840,6 +20815,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086266</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -19937,6 +20917,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119085802</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20034,6 +21019,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086262</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -20141,6 +21131,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119349126</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20238,6 +21233,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086315</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20335,6 +21335,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119261551</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -20433,6 +21438,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119268094</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -20530,6 +21540,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119279562</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -20627,6 +21642,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119279563</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -20724,6 +21744,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297837</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -20821,6 +21846,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120061049</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -20918,6 +21948,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120061051</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -21015,6 +22050,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297574</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -21116,6 +22156,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119085925</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21226,6 +22271,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086306</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21323,6 +22373,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297818</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -21420,6 +22475,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086291</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -21517,6 +22577,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297543</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -21614,6 +22679,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297544</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -21711,6 +22781,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297545</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -21808,6 +22883,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297546</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -21905,6 +22985,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297547</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -22002,6 +23087,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297548</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -22099,6 +23189,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297549</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -22196,6 +23291,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297550</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -22293,6 +23393,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297551</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -22390,6 +23495,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297552</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -22487,6 +23597,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297813</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -22584,6 +23699,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297814</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -22681,6 +23801,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297815</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -22778,6 +23903,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297816</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -22875,6 +24005,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297817</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -22972,6 +24107,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086283</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -23069,6 +24209,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086284</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -23166,6 +24311,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119086285</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -23263,6 +24413,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119261464</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -23360,6 +24515,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119261465</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -23457,6 +24617,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119268028</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -23554,6 +24719,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119268029</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -23651,6 +24821,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119268030</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -23749,6 +24924,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119279560</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -23846,6 +25026,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119279561</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -23943,6 +25128,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297534</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -24040,6 +25230,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297535</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -24137,6 +25332,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297536</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -24234,6 +25434,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297537</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -24331,6 +25536,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297538</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -24428,6 +25638,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297800</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -24525,6 +25740,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297801</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -24622,6 +25842,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297802</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -24719,6 +25944,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297803</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -24816,6 +26046,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297806</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -24913,6 +26148,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297808</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -25010,6 +26250,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297810</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -25116,6 +26361,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297811</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -25213,6 +26463,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297812</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -25311,6 +26566,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119349153</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -25408,6 +26668,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120061007</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -25505,6 +26770,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120061008</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -25612,6 +26882,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118973472</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -25709,6 +26984,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119297555</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -25805,8 +27085,271 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193608</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>